--- a/data/preparation/asics_pre.xlsx
+++ b/data/preparation/asics_pre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/preparation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD31B474-1B85-514E-AB1F-CF0F817A86BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C737AA3-589A-0D4B-8702-97890544CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6200" yWindow="600" windowWidth="22600" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="12680" yWindow="600" windowWidth="25660" windowHeight="21000" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="453">
   <si>
     <t>ID</t>
   </si>
@@ -1412,6 +1412,9 @@
   </si>
   <si>
     <t xml:space="preserve">STRAT </t>
+  </si>
+  <si>
+    <t>PEOPLE</t>
   </si>
 </sst>
 </file>
@@ -1768,156 +1771,156 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N59" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N59" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:N59" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="72"/>
-    <tableColumn id="13" xr3:uid="{6BCF903D-B946-8047-9828-66413972ECB6}" name="Source_type" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="67"/>
-    <tableColumn id="14" xr3:uid="{F85EEC66-2554-3C49-B630-8D54162C843F}" name="Communicator_role" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{6BCF903D-B946-8047-9828-66413972ECB6}" name="Source_type" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{F85EEC66-2554-3C49-B630-8D54162C843F}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N31" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N31" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:N31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{6570256F-1337-8D44-943A-90DA6C5B12A6}" name="Source_type" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{D8933292-E7B8-8743-89DB-DAE4A4A319E9}" name="Communicator_role" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="13" xr3:uid="{6570256F-1337-8D44-943A-90DA6C5B12A6}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="14" xr3:uid="{D8933292-E7B8-8743-89DB-DAE4A4A319E9}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:N37" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:N37" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N37" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{CE985575-B20E-5B41-82ED-541BF3E60C06}" name="Source_type" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{97EBFFD0-1FE7-064A-BC93-83EB00D83017}" name="Communicator_role" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="Communicator_name" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{CE985575-B20E-5B41-82ED-541BF3E60C06}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{97EBFFD0-1FE7-064A-BC93-83EB00D83017}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:N41" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:N41" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:N41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{A142ABD1-0217-3F4A-943B-1E30C4B499DA}" name="Source_type" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{25B63537-0377-344F-A085-9DA95E0D304C}" name="Communicator_role" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="Communicator_name" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{A142ABD1-0217-3F4A-943B-1E30C4B499DA}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{25B63537-0377-344F-A085-9DA95E0D304C}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:N22" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:N22" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:N22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{A2917E69-1A52-5541-A577-5DDC36BEC468}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{AC12DA90-5DA9-1E41-9D3A-5C37C222D798}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="Communicator_name" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{A2917E69-1A52-5541-A577-5DDC36BEC468}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{AC12DA90-5DA9-1E41-9D3A-5C37C222D798}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:N22" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:N22" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{4833111C-1647-E743-BF99-61B814ACEB88}" name="Source_type" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="85"/>
-    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="83"/>
-    <tableColumn id="14" xr3:uid="{2E85A930-D53A-F74B-B953-E9762F261F04}" name="Communicator_role" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="Communicator_name" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{4833111C-1647-E743-BF99-61B814ACEB88}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{2E85A930-D53A-F74B-B953-E9762F261F04}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2722,6 +2725,9 @@
       <c r="D12" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>406</v>
       </c>
@@ -2760,6 +2766,9 @@
       <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>406</v>
       </c>
@@ -3492,6 +3501,9 @@
       <c r="D31" s="1" t="s">
         <v>136</v>
       </c>
+      <c r="E31" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F31" s="1" t="s">
         <v>406</v>
       </c>
@@ -3735,6 +3747,9 @@
       <c r="D37" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="E37" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F37" s="1" t="s">
         <v>406</v>
       </c>
@@ -3773,6 +3788,9 @@
       <c r="D38" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="E38" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F38" s="1" t="s">
         <v>406</v>
       </c>
@@ -3811,6 +3829,9 @@
       <c r="D39" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="E39" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F39" s="1" t="s">
         <v>406</v>
       </c>
@@ -3849,6 +3870,9 @@
       <c r="D40" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="E40" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F40" s="1" t="s">
         <v>406</v>
       </c>
@@ -3966,8 +3990,11 @@
       <c r="C43" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D43" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E43" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>406</v>
@@ -4004,6 +4031,9 @@
       <c r="C44" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D44" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E44" s="1" t="s">
         <v>67</v>
       </c>
@@ -4042,6 +4072,12 @@
       <c r="C45" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F45" s="1" t="s">
         <v>406</v>
       </c>
@@ -4077,6 +4113,12 @@
       <c r="C46" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F46" s="1" t="s">
         <v>406</v>
       </c>
@@ -4235,6 +4277,12 @@
       <c r="C50" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F50" s="1" t="s">
         <v>406</v>
       </c>
@@ -4270,6 +4318,12 @@
       <c r="C51" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D51" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F51" s="1" t="s">
         <v>406</v>
       </c>
@@ -4308,6 +4362,9 @@
       <c r="D52" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="E52" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F52" s="1" t="s">
         <v>406</v>
       </c>
@@ -4346,6 +4403,9 @@
       <c r="D53" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="E53" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F53" s="1" t="s">
         <v>406</v>
       </c>
@@ -4381,6 +4441,12 @@
       <c r="C54" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F54" s="1" t="s">
         <v>406</v>
       </c>
@@ -4416,6 +4482,12 @@
       <c r="C55" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F55" s="1" t="s">
         <v>406</v>
       </c>
@@ -4451,6 +4523,12 @@
       <c r="C56" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F56" s="1" t="s">
         <v>406</v>
       </c>
@@ -4486,6 +4564,12 @@
       <c r="C57" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D57" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F57" s="1" t="s">
         <v>406</v>
       </c>
@@ -4521,6 +4605,12 @@
       <c r="C58" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D58" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="F58" s="1" t="s">
         <v>406</v>
       </c>
@@ -4555,6 +4645,12 @@
       </c>
       <c r="C59" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>406</v>
@@ -5490,7 +5586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>191</v>
       </c>
@@ -8970,7 +9066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>358</v>
       </c>
@@ -9400,6 +9496,12 @@
       <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>40</v>
       </c>
@@ -9435,6 +9537,12 @@
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
@@ -9470,6 +9578,12 @@
       <c r="C4" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
@@ -9505,6 +9619,12 @@
       <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
@@ -9540,6 +9660,12 @@
       <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
@@ -9575,6 +9701,12 @@
       <c r="C7" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
@@ -9610,6 +9742,12 @@
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
@@ -9645,6 +9783,12 @@
       <c r="C9" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>40</v>
       </c>
@@ -9680,6 +9824,12 @@
       <c r="C10" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
       </c>
@@ -9715,6 +9865,12 @@
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
@@ -9750,6 +9906,12 @@
       <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
@@ -9785,6 +9947,12 @@
       <c r="C13" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>40</v>
       </c>
@@ -9820,6 +9988,9 @@
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
@@ -9855,6 +10026,12 @@
       <c r="C15" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
@@ -9890,6 +10067,12 @@
       <c r="C16" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
       </c>
@@ -9925,6 +10108,12 @@
       <c r="C17" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
       </c>
@@ -9960,6 +10149,12 @@
       <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>40</v>
       </c>
@@ -9995,6 +10190,12 @@
       <c r="C19" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
       </c>
@@ -10030,6 +10231,12 @@
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
       </c>
@@ -10065,6 +10272,12 @@
       <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
       </c>
@@ -10099,6 +10312,12 @@
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>40</v>

--- a/data/preparation/asics_pre.xlsx
+++ b/data/preparation/asics_pre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/preparation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C737AA3-589A-0D4B-8702-97890544CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DA0E92-D007-A742-BF08-E0E761DE8F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12680" yWindow="600" windowWidth="25660" windowHeight="21000" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="12680" yWindow="600" windowWidth="25660" windowHeight="21000" activeTab="1" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="455">
   <si>
     <t>ID</t>
   </si>
@@ -468,9 +468,6 @@
   </si>
   <si>
     <t>The results of reforms are powerfully reflected in business performance</t>
-  </si>
-  <si>
-    <t>Last year I mentioned that in Mid-Term Plan 2023, we would aspire to reforms that involve “digging deep and jumping high.” It turned out that in 2021, the results of past reforms were strongly reflected in our business performance, making it a year in which we built solid founda- tions toward future growth. Our biggest accomplishment was seeing through our role as a Gold Partner to the Tokyo 2020 Games. This filled us with a great deal of confidence. Despite almost no opportunities for merchandise sales at venues due to events being held without spectators, over the course of the Games we managed to draw global attention to the ASICS brand through the media. We also saw positive business performance. Net sales returned to the 400 billion yen range and operating income broke 20 billion yen for the first time in five years, with each profit metric going back into positive territory.</t>
   </si>
   <si>
     <t>The health-conscious movement will continue in a post-COVID world</t>
@@ -1415,6 +1412,15 @@
   </si>
   <si>
     <t>PEOPLE</t>
+  </si>
+  <si>
+    <t>Last year I mentioned that in Mid-Term Plan 2023, we would aspire to reforms that involve “digging deep and jumping high.” It turned out that in 2021, the results of past reforms were strongly reflected in our business performance, making it a year in which we built solid founda tions toward future growth. Our biggest accomplishment was seeing through our role as a Gold Partner to the Tokyo 2020 Games. This filled us with a great deal of confidence. Despite almost no opportunities for merchandise sales at venues due to events being held without spectators, over the course of the Games we managed to draw global attention to the ASICS brand through the media. We also saw positive business performance. Net sales returned to the 400 billion yen range and operating income broke 20 billion yen for the first time in five years, with each profit metric going back into positive territory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAKE </t>
+  </si>
+  <si>
+    <t>body_text_list</t>
   </si>
 </sst>
 </file>
@@ -2278,7 +2284,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2293,10 +2299,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -2319,10 +2325,10 @@
         <v>67</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -2337,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>14</v>
@@ -2360,10 +2366,10 @@
         <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -2378,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>14</v>
@@ -2401,10 +2407,10 @@
         <v>68</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -2419,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>14</v>
@@ -2430,7 +2436,7 @@
         <v>73</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -2442,10 +2448,10 @@
         <v>67</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -2460,7 +2466,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>14</v>
@@ -2483,10 +2489,10 @@
         <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -2501,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>14</v>
@@ -2512,7 +2518,7 @@
         <v>75</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
@@ -2524,10 +2530,10 @@
         <v>68</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -2542,7 +2548,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>14</v>
@@ -2553,7 +2559,7 @@
         <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -2565,10 +2571,10 @@
         <v>68</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -2583,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>14</v>
@@ -2606,10 +2612,10 @@
         <v>67</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -2624,7 +2630,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>14</v>
@@ -2647,10 +2653,10 @@
         <v>67</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -2665,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>14</v>
@@ -2688,10 +2694,10 @@
         <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -2706,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>14</v>
@@ -2729,10 +2735,10 @@
         <v>85</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -2747,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>14</v>
@@ -2770,10 +2776,10 @@
         <v>85</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -2788,7 +2794,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>14</v>
@@ -2808,10 +2814,10 @@
         <v>67</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -2826,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>14</v>
@@ -2849,10 +2855,10 @@
         <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -2867,7 +2873,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>14</v>
@@ -2878,7 +2884,7 @@
         <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
@@ -2890,10 +2896,10 @@
         <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -2908,7 +2914,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>14</v>
@@ -2931,10 +2937,10 @@
         <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -2949,7 +2955,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>14</v>
@@ -2972,10 +2978,10 @@
         <v>68</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -2990,7 +2996,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>14</v>
@@ -3013,10 +3019,10 @@
         <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -3031,7 +3037,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>14</v>
@@ -3054,10 +3060,10 @@
         <v>67</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -3072,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>14</v>
@@ -3095,10 +3101,10 @@
         <v>81</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -3113,7 +3119,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>14</v>
@@ -3136,10 +3142,10 @@
         <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -3154,7 +3160,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>14</v>
@@ -3177,10 +3183,10 @@
         <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -3195,7 +3201,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>14</v>
@@ -3218,10 +3224,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -3236,7 +3242,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>14</v>
@@ -3247,7 +3253,7 @@
         <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
@@ -3259,10 +3265,10 @@
         <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -3277,7 +3283,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>14</v>
@@ -3288,7 +3294,7 @@
         <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
@@ -3300,10 +3306,10 @@
         <v>67</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -3318,7 +3324,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>14</v>
@@ -3329,7 +3335,7 @@
         <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
@@ -3341,10 +3347,10 @@
         <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -3359,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>14</v>
@@ -3370,7 +3376,7 @@
         <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>64</v>
@@ -3382,10 +3388,10 @@
         <v>68</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -3400,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>14</v>
@@ -3423,10 +3429,10 @@
         <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -3441,7 +3447,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>14</v>
@@ -3464,10 +3470,10 @@
         <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -3482,7 +3488,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>14</v>
@@ -3505,10 +3511,10 @@
         <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -3523,7 +3529,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>14</v>
@@ -3546,10 +3552,10 @@
         <v>81</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -3564,7 +3570,7 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>14</v>
@@ -3587,10 +3593,10 @@
         <v>81</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -3605,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>14</v>
@@ -3628,10 +3634,10 @@
         <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -3646,7 +3652,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>14</v>
@@ -3669,10 +3675,10 @@
         <v>84</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -3687,7 +3693,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>14</v>
@@ -3710,10 +3716,10 @@
         <v>85</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -3728,7 +3734,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>14</v>
@@ -3751,10 +3757,10 @@
         <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -3769,7 +3775,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>14</v>
@@ -3792,10 +3798,10 @@
         <v>85</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>13</v>
@@ -3810,7 +3816,7 @@
         <v>10</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>14</v>
@@ -3833,10 +3839,10 @@
         <v>67</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>13</v>
@@ -3851,7 +3857,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>14</v>
@@ -3862,7 +3868,7 @@
         <v>116</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>64</v>
@@ -3874,10 +3880,10 @@
         <v>67</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -3892,7 +3898,7 @@
         <v>10</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>14</v>
@@ -3915,10 +3921,10 @@
         <v>81</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>13</v>
@@ -3933,7 +3939,7 @@
         <v>10</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>14</v>
@@ -3950,16 +3956,16 @@
         <v>64</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>13</v>
@@ -3974,7 +3980,7 @@
         <v>10</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>14</v>
@@ -3997,10 +4003,10 @@
         <v>67</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
@@ -4015,7 +4021,7 @@
         <v>10</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>14</v>
@@ -4038,10 +4044,10 @@
         <v>67</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>13</v>
@@ -4056,7 +4062,7 @@
         <v>10</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>14</v>
@@ -4079,10 +4085,10 @@
         <v>67</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>13</v>
@@ -4097,7 +4103,7 @@
         <v>10</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>14</v>
@@ -4108,7 +4114,7 @@
         <v>122</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>64</v>
@@ -4120,10 +4126,10 @@
         <v>81</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
@@ -4138,7 +4144,7 @@
         <v>10</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>14</v>
@@ -4161,10 +4167,10 @@
         <v>85</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -4179,7 +4185,7 @@
         <v>10</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>14</v>
@@ -4190,7 +4196,7 @@
         <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>66</v>
@@ -4202,10 +4208,10 @@
         <v>67</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>13</v>
@@ -4220,7 +4226,7 @@
         <v>10</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>14</v>
@@ -4231,7 +4237,7 @@
         <v>125</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>64</v>
@@ -4243,10 +4249,10 @@
         <v>81</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>13</v>
@@ -4261,7 +4267,7 @@
         <v>10</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>14</v>
@@ -4284,10 +4290,10 @@
         <v>85</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -4302,7 +4308,7 @@
         <v>10</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>14</v>
@@ -4319,16 +4325,16 @@
         <v>64</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>13</v>
@@ -4343,7 +4349,7 @@
         <v>10</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>14</v>
@@ -4366,10 +4372,10 @@
         <v>67</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -4384,7 +4390,7 @@
         <v>10</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>14</v>
@@ -4395,7 +4401,7 @@
         <v>129</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>65</v>
@@ -4407,10 +4413,10 @@
         <v>67</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -4425,7 +4431,7 @@
         <v>10</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>14</v>
@@ -4436,7 +4442,7 @@
         <v>130</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>64</v>
@@ -4448,10 +4454,10 @@
         <v>67</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>13</v>
@@ -4466,7 +4472,7 @@
         <v>10</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>14</v>
@@ -4489,10 +4495,10 @@
         <v>84</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>13</v>
@@ -4507,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>14</v>
@@ -4530,10 +4536,10 @@
         <v>67</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>13</v>
@@ -4548,7 +4554,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>14</v>
@@ -4565,16 +4571,16 @@
         <v>64</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>13</v>
@@ -4589,7 +4595,7 @@
         <v>10</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>14</v>
@@ -4606,16 +4612,16 @@
         <v>64</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>13</v>
@@ -4630,7 +4636,7 @@
         <v>10</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>14</v>
@@ -4641,22 +4647,22 @@
         <v>135</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>13</v>
@@ -4671,7 +4677,7 @@
         <v>10</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>14</v>
@@ -4722,7 +4728,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4737,10 +4743,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -4756,11 +4762,17 @@
       <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -4775,7 +4787,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -4783,7 +4795,7 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>139</v>
@@ -4791,11 +4803,17 @@
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -4810,7 +4828,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -4818,7 +4836,7 @@
     </row>
     <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>140</v>
@@ -4826,11 +4844,17 @@
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -4845,7 +4869,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -4853,19 +4877,25 @@
     </row>
     <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>141</v>
+        <v>452</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -4880,7 +4910,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -4888,19 +4918,25 @@
     </row>
     <row r="6" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F6" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -4915,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -4923,19 +4959,25 @@
     </row>
     <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -4950,7 +4992,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -4958,19 +5000,25 @@
     </row>
     <row r="8" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -4985,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -4993,19 +5041,25 @@
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F9" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -5020,7 +5074,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -5028,19 +5082,25 @@
     </row>
     <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -5055,7 +5115,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -5063,19 +5123,25 @@
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F11" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -5090,7 +5156,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -5098,19 +5164,25 @@
     </row>
     <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F12" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -5125,7 +5197,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -5133,19 +5205,25 @@
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F13" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -5160,7 +5238,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -5168,19 +5246,25 @@
     </row>
     <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F14" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -5195,7 +5279,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -5203,19 +5287,25 @@
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F15" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -5230,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -5238,19 +5328,25 @@
     </row>
     <row r="16" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F16" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -5265,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -5273,19 +5369,25 @@
     </row>
     <row r="17" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F17" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -5300,7 +5402,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -5308,19 +5410,25 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F18" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -5335,7 +5443,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -5343,19 +5451,25 @@
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F19" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -5370,7 +5484,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -5378,19 +5492,25 @@
     </row>
     <row r="20" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F20" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -5405,7 +5525,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -5413,19 +5533,25 @@
     </row>
     <row r="21" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F21" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -5440,7 +5566,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -5448,19 +5574,25 @@
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F22" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -5475,7 +5607,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -5483,19 +5615,25 @@
     </row>
     <row r="23" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F23" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -5510,7 +5648,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>16</v>
@@ -5518,19 +5656,25 @@
     </row>
     <row r="24" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F24" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -5545,7 +5689,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>16</v>
@@ -5553,19 +5697,25 @@
     </row>
     <row r="25" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>454</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -5580,7 +5730,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>16</v>
@@ -5588,19 +5738,25 @@
     </row>
     <row r="26" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -5615,7 +5771,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>16</v>
@@ -5623,19 +5779,25 @@
     </row>
     <row r="27" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F27" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -5650,7 +5812,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>16</v>
@@ -5658,19 +5820,25 @@
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F28" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -5685,7 +5853,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>16</v>
@@ -5693,19 +5861,25 @@
     </row>
     <row r="29" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -5720,7 +5894,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>16</v>
@@ -5728,19 +5902,25 @@
     </row>
     <row r="30" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F30" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -5755,7 +5935,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>16</v>
@@ -5763,19 +5943,25 @@
     </row>
     <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F31" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -5790,7 +5976,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>16</v>
@@ -5845,7 +6031,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -5860,10 +6046,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -5874,7 +6060,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>64</v>
@@ -5883,7 +6069,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -5898,7 +6084,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -5906,10 +6092,10 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
@@ -5918,7 +6104,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5933,7 +6119,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -5941,10 +6127,10 @@
     </row>
     <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
@@ -5953,7 +6139,7 @@
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -5968,7 +6154,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -5976,10 +6162,10 @@
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
@@ -5988,7 +6174,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -6003,7 +6189,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -6011,10 +6197,10 @@
     </row>
     <row r="6" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
@@ -6023,7 +6209,7 @@
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -6038,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -6046,10 +6232,10 @@
     </row>
     <row r="7" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>65</v>
@@ -6058,7 +6244,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -6073,7 +6259,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -6081,7 +6267,7 @@
     </row>
     <row r="8" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -6090,7 +6276,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -6105,7 +6291,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -6113,10 +6299,10 @@
     </row>
     <row r="9" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
@@ -6125,7 +6311,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -6140,7 +6326,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -6148,10 +6334,10 @@
     </row>
     <row r="10" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
@@ -6160,7 +6346,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -6175,7 +6361,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -6183,10 +6369,10 @@
     </row>
     <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
@@ -6195,7 +6381,7 @@
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -6210,7 +6396,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -6218,10 +6404,10 @@
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>65</v>
@@ -6230,7 +6416,7 @@
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -6245,7 +6431,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -6253,10 +6439,10 @@
     </row>
     <row r="13" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
@@ -6265,7 +6451,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -6280,7 +6466,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -6288,10 +6474,10 @@
     </row>
     <row r="14" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
@@ -6300,7 +6486,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -6315,7 +6501,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -6323,10 +6509,10 @@
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
@@ -6335,7 +6521,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -6350,7 +6536,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -6358,10 +6544,10 @@
     </row>
     <row r="16" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
@@ -6370,7 +6556,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -6385,7 +6571,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -6393,10 +6579,10 @@
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>65</v>
@@ -6405,7 +6591,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -6420,7 +6606,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -6428,10 +6614,10 @@
     </row>
     <row r="18" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
@@ -6440,7 +6626,7 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -6455,7 +6641,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -6463,10 +6649,10 @@
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
@@ -6475,7 +6661,7 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -6490,7 +6676,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -6498,10 +6684,10 @@
     </row>
     <row r="20" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
@@ -6510,7 +6696,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -6525,7 +6711,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -6533,10 +6719,10 @@
     </row>
     <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>65</v>
@@ -6545,7 +6731,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -6560,7 +6746,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -6568,10 +6754,10 @@
     </row>
     <row r="22" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
@@ -6580,7 +6766,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -6595,7 +6781,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -6603,10 +6789,10 @@
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>65</v>
@@ -6615,7 +6801,7 @@
         <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -6630,7 +6816,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>16</v>
@@ -6638,10 +6824,10 @@
     </row>
     <row r="24" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
@@ -6650,7 +6836,7 @@
         <v>40</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -6665,7 +6851,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>16</v>
@@ -6673,10 +6859,10 @@
     </row>
     <row r="25" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
@@ -6685,7 +6871,7 @@
         <v>40</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -6700,7 +6886,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>16</v>
@@ -6708,10 +6894,10 @@
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>65</v>
@@ -6720,7 +6906,7 @@
         <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -6735,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>16</v>
@@ -6743,10 +6929,10 @@
     </row>
     <row r="27" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
@@ -6755,7 +6941,7 @@
         <v>40</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -6770,7 +6956,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>16</v>
@@ -6778,10 +6964,10 @@
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
@@ -6790,7 +6976,7 @@
         <v>40</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -6805,7 +6991,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>16</v>
@@ -6813,10 +6999,10 @@
     </row>
     <row r="29" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
@@ -6825,7 +7011,7 @@
         <v>40</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -6840,7 +7026,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>16</v>
@@ -6848,10 +7034,10 @@
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>65</v>
@@ -6860,7 +7046,7 @@
         <v>40</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -6875,7 +7061,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>16</v>
@@ -6883,10 +7069,10 @@
     </row>
     <row r="31" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
@@ -6895,7 +7081,7 @@
         <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -6910,7 +7096,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>16</v>
@@ -6918,10 +7104,10 @@
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>65</v>
@@ -6930,7 +7116,7 @@
         <v>40</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -6945,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>16</v>
@@ -6953,10 +7139,10 @@
     </row>
     <row r="33" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
@@ -6965,7 +7151,7 @@
         <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -6980,7 +7166,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>16</v>
@@ -6988,10 +7174,10 @@
     </row>
     <row r="34" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>64</v>
@@ -7000,7 +7186,7 @@
         <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -7015,7 +7201,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>16</v>
@@ -7023,10 +7209,10 @@
     </row>
     <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>64</v>
@@ -7035,7 +7221,7 @@
         <v>40</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -7050,7 +7236,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>16</v>
@@ -7058,10 +7244,10 @@
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
@@ -7070,7 +7256,7 @@
         <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -7085,7 +7271,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>16</v>
@@ -7093,10 +7279,10 @@
     </row>
     <row r="37" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>64</v>
@@ -7105,7 +7291,7 @@
         <v>40</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -7120,7 +7306,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>16</v>
@@ -7175,7 +7361,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -7190,10 +7376,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -7204,16 +7390,16 @@
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -7228,27 +7414,27 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -7263,27 +7449,27 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -7298,27 +7484,27 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -7333,27 +7519,27 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -7368,27 +7554,27 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -7403,27 +7589,27 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -7438,27 +7624,27 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -7473,27 +7659,27 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="248" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -7508,27 +7694,27 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -7543,27 +7729,27 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -7578,27 +7764,27 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -7613,27 +7799,27 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="272" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -7648,27 +7834,27 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -7683,27 +7869,27 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -7718,27 +7904,27 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -7753,27 +7939,27 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -7788,27 +7974,27 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -7823,27 +8009,27 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -7858,27 +8044,27 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -7893,27 +8079,27 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -7928,27 +8114,27 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -7963,27 +8149,27 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="323" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -7998,27 +8184,27 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -8033,27 +8219,27 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="356" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -8068,27 +8254,27 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -8103,27 +8289,27 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -8138,27 +8324,27 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -8173,27 +8359,27 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -8208,27 +8394,27 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -8243,27 +8429,27 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -8278,27 +8464,27 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -8313,15 +8499,15 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
@@ -8330,10 +8516,10 @@
         <v>65</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -8348,27 +8534,27 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -8383,27 +8569,27 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -8418,27 +8604,27 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -8453,27 +8639,27 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>13</v>
@@ -8488,27 +8674,27 @@
         <v>10</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>13</v>
@@ -8523,27 +8709,27 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -8558,27 +8744,27 @@
         <v>10</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>13</v>
@@ -8593,10 +8779,10 @@
         <v>10</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -8645,7 +8831,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -8660,10 +8846,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -8674,7 +8860,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
@@ -8689,7 +8875,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -8704,7 +8890,7 @@
         <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -8712,10 +8898,10 @@
     </row>
     <row r="3" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>64</v>
@@ -8730,7 +8916,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -8745,7 +8931,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -8753,10 +8939,10 @@
     </row>
     <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>65</v>
@@ -8765,7 +8951,7 @@
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -8780,7 +8966,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -8788,10 +8974,10 @@
     </row>
     <row r="5" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -8800,7 +8986,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -8815,7 +9001,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -8823,10 +9009,10 @@
     </row>
     <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
@@ -8835,7 +9021,7 @@
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -8850,7 +9036,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -8858,10 +9044,10 @@
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
@@ -8870,7 +9056,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -8885,7 +9071,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -8893,10 +9079,10 @@
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -8905,7 +9091,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -8920,7 +9106,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -8928,10 +9114,10 @@
     </row>
     <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
@@ -8940,7 +9126,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -8955,7 +9141,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -8963,10 +9149,10 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>65</v>
@@ -8975,7 +9161,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -8990,7 +9176,7 @@
         <v>18</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -8998,10 +9184,10 @@
     </row>
     <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
@@ -9010,7 +9196,7 @@
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -9025,7 +9211,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -9033,10 +9219,10 @@
     </row>
     <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
@@ -9045,7 +9231,7 @@
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -9060,7 +9246,7 @@
         <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -9068,10 +9254,10 @@
     </row>
     <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
@@ -9080,7 +9266,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -9095,7 +9281,7 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -9103,10 +9289,10 @@
     </row>
     <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
@@ -9115,7 +9301,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -9130,7 +9316,7 @@
         <v>18</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -9138,10 +9324,10 @@
     </row>
     <row r="15" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>64</v>
@@ -9150,7 +9336,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -9165,7 +9351,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -9173,10 +9359,10 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>65</v>
@@ -9185,7 +9371,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -9200,7 +9386,7 @@
         <v>18</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -9208,10 +9394,10 @@
     </row>
     <row r="17" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
@@ -9220,7 +9406,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -9235,7 +9421,7 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -9243,10 +9429,10 @@
     </row>
     <row r="18" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
@@ -9255,7 +9441,7 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -9270,7 +9456,7 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -9278,10 +9464,10 @@
     </row>
     <row r="19" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>64</v>
@@ -9290,7 +9476,7 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -9305,7 +9491,7 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -9313,10 +9499,10 @@
     </row>
     <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>65</v>
@@ -9325,7 +9511,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -9340,7 +9526,7 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -9348,10 +9534,10 @@
     </row>
     <row r="21" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
@@ -9360,7 +9546,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -9375,7 +9561,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -9383,10 +9569,10 @@
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
@@ -9395,7 +9581,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -9410,7 +9596,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -9462,7 +9648,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -9477,10 +9663,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -9491,7 +9677,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
@@ -9506,7 +9692,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -9521,7 +9707,7 @@
         <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -9529,10 +9715,10 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
@@ -9547,7 +9733,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -9562,7 +9748,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -9570,10 +9756,10 @@
     </row>
     <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
@@ -9588,7 +9774,7 @@
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -9603,7 +9789,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -9611,10 +9797,10 @@
     </row>
     <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -9629,7 +9815,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -9644,7 +9830,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -9652,10 +9838,10 @@
     </row>
     <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
@@ -9670,7 +9856,7 @@
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -9685,7 +9871,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -9693,10 +9879,10 @@
     </row>
     <row r="7" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
@@ -9711,7 +9897,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -9726,7 +9912,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -9734,10 +9920,10 @@
     </row>
     <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -9752,7 +9938,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -9767,7 +9953,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -9775,10 +9961,10 @@
     </row>
     <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
@@ -9793,7 +9979,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -9808,7 +9994,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -9816,10 +10002,10 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>65</v>
@@ -9834,7 +10020,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -9849,7 +10035,7 @@
         <v>18</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -9857,10 +10043,10 @@
     </row>
     <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
@@ -9875,7 +10061,7 @@
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -9890,7 +10076,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -9898,10 +10084,10 @@
     </row>
     <row r="12" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
@@ -9916,7 +10102,7 @@
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -9931,7 +10117,7 @@
         <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -9939,10 +10125,10 @@
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>65</v>
@@ -9957,7 +10143,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -9972,7 +10158,7 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -9980,10 +10166,10 @@
     </row>
     <row r="14" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
@@ -9995,7 +10181,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -10010,7 +10196,7 @@
         <v>18</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -10018,10 +10204,10 @@
     </row>
     <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>64</v>
@@ -10036,7 +10222,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -10051,7 +10237,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -10059,10 +10245,10 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>65</v>
@@ -10077,7 +10263,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -10092,7 +10278,7 @@
         <v>18</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -10100,10 +10286,10 @@
     </row>
     <row r="17" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
@@ -10118,7 +10304,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -10133,7 +10319,7 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -10141,16 +10327,16 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>67</v>
@@ -10159,7 +10345,7 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -10174,7 +10360,7 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -10182,10 +10368,10 @@
     </row>
     <row r="19" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>64</v>
@@ -10200,7 +10386,7 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -10215,7 +10401,7 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -10223,16 +10409,16 @@
     </row>
     <row r="20" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>67</v>
@@ -10241,7 +10427,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -10256,7 +10442,7 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -10264,10 +10450,10 @@
     </row>
     <row r="21" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
@@ -10282,7 +10468,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -10297,7 +10483,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -10305,10 +10491,10 @@
     </row>
     <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
@@ -10323,7 +10509,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -10338,7 +10524,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>

--- a/data/preparation/asics_pre.xlsx
+++ b/data/preparation/asics_pre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/preparation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DA0E92-D007-A742-BF08-E0E761DE8F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41523762-ACAD-8E4C-B316-081B3B55293F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12680" yWindow="600" windowWidth="25660" windowHeight="21000" activeTab="1" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="456">
   <si>
     <t>ID</t>
   </si>
@@ -725,9 +725,6 @@
     <t>Regarding intangible assets, it is important that we surely protect the brand and increase its value. This is supported by human capital and intellectual capital. It is said that business is people. Improving the environment to attract many highly talented human resources to ASICS and enable them to work leveraging diverse work styles is also a duty I have as a top manegement. We would like to collect human resources to ensure that ASICS stays an organization where human resources can grow. In addition, ASICS operates its business with a focus on innovation, so we are fully aware of intellectual property. We will acquire patents and rights while proceeding with projects, and intellectual properties are among the arrows in our quiver.</t>
   </si>
   <si>
-    <t>The Environment, Human Rights, and Sustainable Procurement are Central to Managemen</t>
-  </si>
-  <si>
     <t>It is not possible to play sports on a scorching planet. Therefore, we will accelerate initiatives to address climate change by positioning the protection of the environment of a planet where playing sports is possible as an important task that is vital to the survival of ASICS. ASICS advances initiatives by sharing a specific roadmap toward the achievement of net-zero emissions from its entire supply chain by 2050. Once a year, I visit production factories, which have an extremely important place in the supply chain, to check their actual conditions in person. We will take initiatives to protect the human rights of workers and improve their work environment, such as streamlining production through mechanization, while also establishing systems and operations that prevent child labor, excessive work hours, and other problems. In addition, to protect the global environment, we will accelerate the shift of our production factories to renewable energy.</t>
   </si>
   <si>
@@ -791,10 +788,6 @@
     <t>Management System</t>
   </si>
   <si>
-    <t>To transform to a Global Integrated Enterprise, we have made significant changes to our management decision-making mechanisms. The CEOs of our regional operating companies have been placed directly under the President, and starting this year our management meetings will be held as global management meetings with members from key overseas regional operating companies also taking part. To reinvigorate communication between regional operating companies and facilitate overall optimization, these meetings will be held in English. In addition, twice a year we will hold a Global Summit at our Kobe head office to gather the CEOs of all the regional operating companies in one place. These will be a chance to thoroughly discuss a range of topics including branding, the supply chain and our global
-talent strategy.</t>
-  </si>
-  <si>
     <t>The members responsible for this management structure have also undergone a shakeup, and close to 60% of the management team have assumed new leadership roles. The management team, which now has more women and overseas members, is not only younger and more diverse but also better equipped than ever to drive our digital, services and global priorities. Under this management system, we will make dynamic use of IT platforms, data and talent worldwide as a GIE.</t>
   </si>
   <si>
@@ -802,9 +795,6 @@
   </si>
   <si>
     <t>For the human resources supporting ASICS as a GIE, we aim to create a structure where people with various specialties in different countries have avenues for success that are not limited to their own regions. Instead, we will establish regions where experts in each field gather as global heads from which they will oversee global efforts.</t>
-  </si>
-  <si>
-    <t>For example, until now we have assembled a team of 70 personnel in Europe who are well versed in business operations, systems and project management to link our IT systems globally. By rolling out systems from this base, we have managed to build IT systems that are standardized across the Group. In the areas of e-commerce and software, our Boston, USA–based ASICS Digital oversees the global implementation of digital technologies, while race registration is handled by our team in Canada. In terms of products, at the ASICS Creation Center that was established in Boston this year, personnel familiar with trends in the European and U.S. markets will collaborate organically with our Institute of Sports Science in Japan and other categories. Our style is to look at and oversee a particular field globally from the most appropriate region instead of always looking at the global picture from Japan. This style applies not only to digital technologies but also to category, human resources, legal affairs, supply chain management and so on. I believe our transformation to a Global Integrated Enterprise is quite a challenging endeavor. However, I regard it as an essential transformation as ASICS’ next step to becoming a leading global company in the truest sense. On top of the strengths that ASICS has always enjoyed, such as the quality and functionality of its products, the teamwork of its employees and brand loyalty, if we can gain the ability to improve productivity by incorporating new innovations emerging around the world, a bright future for ASICS is assured. As someone who is Japanese but has built a career in a multinational environment, I think I can contribute in significant ways to this transformation and it is something that I will push for with zeal</t>
   </si>
   <si>
     <t>Digital Technology and the OneASICS Strategy</t>
@@ -1343,11 +1333,6 @@
     <t>Meanwhile, in markets such as India and Southeast Asia that are expected to enjoy high growth, we will promote ASICS’ philosophy along with brand recognition by dedicating human and financial resources through the dispatch of young talent personnel, investments in stores and other efforts. India, in particular, is highly attractive not only for its potential as a market but also because it is home to many tech-savvy workers with world-class skills. ASICS is the main sponsor of the Mumbai Marathon, and I have personally traveled there to strengthen our ties with the local race registration company. Outside India, there are many other regions with strong prospects for market growth such as Indonesia, and we are making progress in market development while considering the adoption of prior examples from other regions. For example, in Australia, where we have established ourselves as a brand with a leading market share, ASICS shoes are highly regarded from a medical standpoint, and one idea is to take our approach in Australia of spreading recognition of the ASICS brand in conjunction with our Sound Mind, Sound Body philosophy and expanding it to other regions. Rather than being directed from the Head Quarter, our aim is for each regional operating company, which is familiar with its own market characteristics, to pursue measures autonomously, drive regional growth and, as a result, contribute to the global growth of ASICS.</t>
   </si>
   <si>
-    <t>ASICS has evolved as a digitally driven company at a global scale, and even on the
-operational front, we pursue operational excellence in an effort to boost productivity through the full use of AI in supply chain management, including R&amp;D and inventory control. With respect to customers, over the past three years we have increased the number of direct points of contact, and direct-to-consumer (DTC) sales have risen as a percentage of total sales. Underpinning these efforts is our OneASICS loyalty program. The number of OneASICS members still stands at only 15 million and involves elements designed to attract customers such as the granting of points and free shipping, but in the future, we will further improve
-and expand the service offerings by utilizing the data we have accumulated to date, including purchase histories, training results and race entry history. For example, in addition to utilizing OneASICS for daily training or to sign up for sports events with friends, we will expand tools designed for exercise or to boost motivation targeting middle-aged and senior customers who want to build up their training due to concerns about declining physical fitness. I think this precisely represents the promotion of ASICS’ Sound Mind, Sound Body philosophy. We aim to increase the number of OneASICS members to 30 million and raise the DTC sales ratio to 40% while expanding the number of facility users and holders of OneASICS bonds. ASICS builds databases of people who enjoy a wide range of sports in addition to running, and by coordinating with partners familiar with other areas such as the tracking of medical and training data, we can link that data to improvements in marketing, products and services. By doing so, our aim is to change the current impression that many people have of ASICS as a shoes company to a “company that promotes Sound Mind and Sound Body.”</t>
-  </si>
-  <si>
     <t>We have begun to see the results of building and implementing the category-based management system we began in 2019, and today ASICS is demonstrating a strong competitive advantage globally based on its dominant products. In MTP 2026, which began in 2024, we will pool our strengths to promote the Global × Digital approach under a new management structure, and strive to meet our targets.</t>
   </si>
   <si>
@@ -1421,6 +1406,22 @@
   </si>
   <si>
     <t>body_text_list</t>
+  </si>
+  <si>
+    <t>The Environment, Human Rights, and Sustainable Procurement are Central to Management</t>
+  </si>
+  <si>
+    <t>JPN22A03-03</t>
+  </si>
+  <si>
+    <t>To transform to a Global Integrated Enterprise, we have made significant changes to our management decision-making mechanisms. The CEOs of our regional operating companies have been placed directly under the President, and starting this year our management meetings will be held as global management meetings with members from key overseas regional operating companies also taking part. To reinvigorate communication between regional operating companies and facilitate overall optimization, these meetings will be held in English. In addition, twice a year we will hold a Global Summit at our Kobe head office to gather the CEOs of all the regional operating companies in one place. These will be a chance to thoroughly discuss a range of topics including branding, the supply chain and our global talent strategy.</t>
+  </si>
+  <si>
+    <t>For example, until now we have assembled a team of 70 personnel in Europe who are well versed in business operations, systems and project management to link our IT systems globally. By rolling out systems from this base, we have managed to build IT systems that are standardized across the Group. In the areas of e-commerce and software, our Boston, USA–based ASICS Digital oversees the global implementation of digital technologies, while race registration is handled by our team in Canada. In terms of products, at the ASICS Creation Center that was established in Boston this year, personnel familiar with trends in the European and U.S. markets will collaborate organically with our Institute of Sports Science in Japan and other categories. Our style is to look at and oversee a particular field globally from the most appropriate region instead of always looking at the global picture from Japan. This style applies not only to digital technologies but also to category, human resources, legal affairs, supply chain management and so on. I believe our transformation to a Global Integrated Enterprise is quite a challenging endeavor. However, I regard it as an essential transformation as ASICS’ next step to becoming a leading global company in the truest sense. On top of the strengths that ASICS has always enjoyed, such as the quality and functionality of its products, the teamwork of its employees and brand loyalty, if we can gain the ability to improve productivity by incorporating new innovations emerging around the world, a bright future for ASICS is assured. As someone who is Japanese but has built a career in a multinational environment, I think I can contribute in significant ways to this transformation and it is something that I will push for with zeal.</t>
+  </si>
+  <si>
+    <t>ASICS has evolved as a digitally driven company at a global scale, and even on the
+operational front, we pursue operational excellence in an effort to boost productivity through the full use of AI in supply chain management, including R&amp;D and inventory control. With respect to customers, over the past three years we have increased the number of direct points of contact, and direct-to-consumer (DTC) sales have risen as a percentage of total sales. Underpinning these efforts is our OneASICS loyalty program. The number of OneASICS members still stands at only 15 million and involves elements designed to attract customers such as the granting of points and free shipping, but in the future, we will further improve and expand the service offerings by utilizing the data we have accumulated to date, including purchase histories, training results and race entry history. For example, in addition to utilizing OneASICS for daily training or to sign up for sports events with friends, we will expand tools designed for exercise or to boost motivation targeting middle-aged and senior customers who want to build up their training due to concerns about declining physical fitness. I think this precisely represents the promotion of ASICS’ Sound Mind, Sound Body philosophy. We aim to increase the number of OneASICS members to 30 million and raise the DTC sales ratio to 40% while expanding the number of facility users and holders of OneASICS bonds. ASICS builds databases of people who enjoy a wide range of sports in addition to running, and by coordinating with partners familiar with other areas such as the tracking of medical and training data, we can link that data to improvements in marketing, products and services. By doing so, our aim is to change the current impression that many people have of ASICS as a shoes company to a “company that promotes Sound Mind and Sound Body.”</t>
   </si>
 </sst>
 </file>
@@ -2284,7 +2285,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2299,10 +2300,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -2325,10 +2326,10 @@
         <v>67</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -2343,7 +2344,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>14</v>
@@ -2366,10 +2367,10 @@
         <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -2384,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>14</v>
@@ -2407,10 +2408,10 @@
         <v>68</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -2425,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>14</v>
@@ -2436,7 +2437,7 @@
         <v>73</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -2448,10 +2449,10 @@
         <v>67</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -2466,7 +2467,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>14</v>
@@ -2489,10 +2490,10 @@
         <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -2507,7 +2508,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>14</v>
@@ -2518,7 +2519,7 @@
         <v>75</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
@@ -2530,10 +2531,10 @@
         <v>68</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -2548,7 +2549,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>14</v>
@@ -2559,7 +2560,7 @@
         <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -2571,10 +2572,10 @@
         <v>68</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -2589,7 +2590,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>14</v>
@@ -2612,10 +2613,10 @@
         <v>67</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -2630,7 +2631,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>14</v>
@@ -2653,10 +2654,10 @@
         <v>67</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -2671,7 +2672,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>14</v>
@@ -2694,10 +2695,10 @@
         <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -2712,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>14</v>
@@ -2735,10 +2736,10 @@
         <v>85</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -2753,7 +2754,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>14</v>
@@ -2776,10 +2777,10 @@
         <v>85</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -2794,7 +2795,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>14</v>
@@ -2814,10 +2815,10 @@
         <v>67</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -2832,7 +2833,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>14</v>
@@ -2855,10 +2856,10 @@
         <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -2873,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>14</v>
@@ -2884,7 +2885,7 @@
         <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
@@ -2896,10 +2897,10 @@
         <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -2914,7 +2915,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>14</v>
@@ -2937,10 +2938,10 @@
         <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -2955,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>14</v>
@@ -2978,10 +2979,10 @@
         <v>68</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -2996,7 +2997,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>14</v>
@@ -3019,10 +3020,10 @@
         <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -3037,7 +3038,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>14</v>
@@ -3060,10 +3061,10 @@
         <v>67</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -3078,7 +3079,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>14</v>
@@ -3101,10 +3102,10 @@
         <v>81</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -3119,7 +3120,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>14</v>
@@ -3142,10 +3143,10 @@
         <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -3160,7 +3161,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>14</v>
@@ -3183,10 +3184,10 @@
         <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -3201,7 +3202,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>14</v>
@@ -3224,10 +3225,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -3242,7 +3243,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>14</v>
@@ -3253,7 +3254,7 @@
         <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
@@ -3265,10 +3266,10 @@
         <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -3283,7 +3284,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>14</v>
@@ -3294,7 +3295,7 @@
         <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
@@ -3306,10 +3307,10 @@
         <v>67</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -3324,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>14</v>
@@ -3335,7 +3336,7 @@
         <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
@@ -3347,10 +3348,10 @@
         <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -3365,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>14</v>
@@ -3376,7 +3377,7 @@
         <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>64</v>
@@ -3388,10 +3389,10 @@
         <v>68</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -3406,7 +3407,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>14</v>
@@ -3429,10 +3430,10 @@
         <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -3447,7 +3448,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>14</v>
@@ -3470,10 +3471,10 @@
         <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -3488,7 +3489,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>14</v>
@@ -3511,10 +3512,10 @@
         <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -3529,7 +3530,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>14</v>
@@ -3552,10 +3553,10 @@
         <v>81</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -3570,7 +3571,7 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>14</v>
@@ -3593,10 +3594,10 @@
         <v>81</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -3611,7 +3612,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>14</v>
@@ -3634,10 +3635,10 @@
         <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -3652,7 +3653,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>14</v>
@@ -3675,10 +3676,10 @@
         <v>84</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -3693,7 +3694,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>14</v>
@@ -3716,10 +3717,10 @@
         <v>85</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -3734,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>14</v>
@@ -3757,10 +3758,10 @@
         <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -3775,7 +3776,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>14</v>
@@ -3798,10 +3799,10 @@
         <v>85</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>13</v>
@@ -3816,7 +3817,7 @@
         <v>10</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>14</v>
@@ -3839,10 +3840,10 @@
         <v>67</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>13</v>
@@ -3857,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>14</v>
@@ -3868,7 +3869,7 @@
         <v>116</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>64</v>
@@ -3880,10 +3881,10 @@
         <v>67</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -3898,7 +3899,7 @@
         <v>10</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>14</v>
@@ -3921,10 +3922,10 @@
         <v>81</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>13</v>
@@ -3939,7 +3940,7 @@
         <v>10</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>14</v>
@@ -3956,16 +3957,16 @@
         <v>64</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>13</v>
@@ -3980,7 +3981,7 @@
         <v>10</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>14</v>
@@ -4003,10 +4004,10 @@
         <v>67</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
@@ -4021,7 +4022,7 @@
         <v>10</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>14</v>
@@ -4044,10 +4045,10 @@
         <v>67</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>13</v>
@@ -4062,7 +4063,7 @@
         <v>10</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>14</v>
@@ -4085,10 +4086,10 @@
         <v>67</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>13</v>
@@ -4103,7 +4104,7 @@
         <v>10</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>14</v>
@@ -4114,7 +4115,7 @@
         <v>122</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>64</v>
@@ -4126,10 +4127,10 @@
         <v>81</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
@@ -4144,7 +4145,7 @@
         <v>10</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>14</v>
@@ -4167,10 +4168,10 @@
         <v>85</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -4185,7 +4186,7 @@
         <v>10</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>14</v>
@@ -4196,7 +4197,7 @@
         <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>66</v>
@@ -4208,10 +4209,10 @@
         <v>67</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>13</v>
@@ -4226,7 +4227,7 @@
         <v>10</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>14</v>
@@ -4237,7 +4238,7 @@
         <v>125</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>64</v>
@@ -4249,10 +4250,10 @@
         <v>81</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>13</v>
@@ -4267,7 +4268,7 @@
         <v>10</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>14</v>
@@ -4290,10 +4291,10 @@
         <v>85</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -4308,7 +4309,7 @@
         <v>10</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>14</v>
@@ -4325,16 +4326,16 @@
         <v>64</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>13</v>
@@ -4349,7 +4350,7 @@
         <v>10</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>14</v>
@@ -4372,10 +4373,10 @@
         <v>67</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -4390,7 +4391,7 @@
         <v>10</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>14</v>
@@ -4401,7 +4402,7 @@
         <v>129</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>65</v>
@@ -4413,10 +4414,10 @@
         <v>67</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -4431,7 +4432,7 @@
         <v>10</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>14</v>
@@ -4442,7 +4443,7 @@
         <v>130</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>64</v>
@@ -4454,10 +4455,10 @@
         <v>67</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>13</v>
@@ -4472,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>14</v>
@@ -4495,10 +4496,10 @@
         <v>84</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>13</v>
@@ -4513,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>14</v>
@@ -4536,10 +4537,10 @@
         <v>67</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>13</v>
@@ -4554,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>14</v>
@@ -4571,16 +4572,16 @@
         <v>64</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>13</v>
@@ -4595,7 +4596,7 @@
         <v>10</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>14</v>
@@ -4612,16 +4613,16 @@
         <v>64</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>13</v>
@@ -4636,7 +4637,7 @@
         <v>10</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>14</v>
@@ -4647,22 +4648,22 @@
         <v>135</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>13</v>
@@ -4677,7 +4678,7 @@
         <v>10</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>14</v>
@@ -4728,7 +4729,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4743,10 +4744,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -4769,10 +4770,10 @@
         <v>67</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -4787,7 +4788,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -4810,10 +4811,10 @@
         <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -4828,7 +4829,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -4851,10 +4852,10 @@
         <v>67</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -4869,7 +4870,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -4880,7 +4881,7 @@
         <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -4892,10 +4893,10 @@
         <v>68</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -4910,7 +4911,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -4933,10 +4934,10 @@
         <v>67</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -4951,7 +4952,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -4974,10 +4975,10 @@
         <v>67</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -4992,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -5015,10 +5016,10 @@
         <v>81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -5033,7 +5034,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -5056,10 +5057,10 @@
         <v>68</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -5074,7 +5075,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -5097,10 +5098,10 @@
         <v>68</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -5115,7 +5116,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -5138,10 +5139,10 @@
         <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -5156,7 +5157,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -5179,10 +5180,10 @@
         <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -5197,7 +5198,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -5220,10 +5221,10 @@
         <v>67</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -5238,7 +5239,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -5261,10 +5262,10 @@
         <v>68</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -5279,7 +5280,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -5302,10 +5303,10 @@
         <v>67</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -5320,7 +5321,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -5343,10 +5344,10 @@
         <v>67</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -5361,7 +5362,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -5384,10 +5385,10 @@
         <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -5402,7 +5403,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -5425,10 +5426,10 @@
         <v>67</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -5443,7 +5444,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -5466,10 +5467,10 @@
         <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -5484,7 +5485,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -5507,10 +5508,10 @@
         <v>67</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -5525,7 +5526,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -5548,10 +5549,10 @@
         <v>67</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -5566,7 +5567,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -5589,10 +5590,10 @@
         <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -5607,7 +5608,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -5624,16 +5625,16 @@
         <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -5648,7 +5649,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>16</v>
@@ -5671,10 +5672,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -5689,7 +5690,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>16</v>
@@ -5703,19 +5704,19 @@
         <v>160</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -5730,7 +5731,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>16</v>
@@ -5747,16 +5748,16 @@
         <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -5771,7 +5772,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>16</v>
@@ -5788,16 +5789,16 @@
         <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -5812,7 +5813,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>16</v>
@@ -5835,10 +5836,10 @@
         <v>67</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -5853,7 +5854,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>16</v>
@@ -5876,10 +5877,10 @@
         <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -5894,7 +5895,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>16</v>
@@ -5917,10 +5918,10 @@
         <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -5935,7 +5936,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>16</v>
@@ -5958,10 +5959,10 @@
         <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -5976,7 +5977,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>16</v>
@@ -6031,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -6046,10 +6047,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -6065,11 +6066,17 @@
       <c r="C2" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -6084,7 +6091,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -6092,7 +6099,7 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>197</v>
@@ -6100,11 +6107,17 @@
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -6119,7 +6132,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -6127,7 +6140,7 @@
     </row>
     <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>198</v>
@@ -6135,11 +6148,17 @@
       <c r="C4" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -6154,7 +6173,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -6162,7 +6181,7 @@
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>199</v>
@@ -6170,11 +6189,17 @@
       <c r="C5" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -6189,7 +6214,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -6197,7 +6222,7 @@
     </row>
     <row r="6" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>200</v>
@@ -6205,11 +6230,17 @@
       <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -6224,7 +6255,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -6232,7 +6263,7 @@
     </row>
     <row r="7" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>201</v>
@@ -6240,11 +6271,17 @@
       <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -6259,24 +6296,33 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -6291,7 +6337,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -6299,7 +6345,7 @@
     </row>
     <row r="9" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>203</v>
@@ -6307,11 +6353,17 @@
       <c r="C9" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -6326,15 +6378,15 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>204</v>
@@ -6342,11 +6394,17 @@
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -6361,7 +6419,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -6369,7 +6427,7 @@
     </row>
     <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>272</v>
+        <v>452</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>205</v>
@@ -6377,11 +6435,17 @@
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -6396,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -6404,7 +6468,7 @@
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>206</v>
@@ -6412,11 +6476,17 @@
       <c r="C12" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -6431,7 +6501,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -6439,7 +6509,7 @@
     </row>
     <row r="13" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>207</v>
@@ -6447,11 +6517,17 @@
       <c r="C13" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -6466,7 +6542,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -6474,7 +6550,7 @@
     </row>
     <row r="14" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>208</v>
@@ -6482,11 +6558,17 @@
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -6501,7 +6583,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -6509,7 +6591,7 @@
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>209</v>
@@ -6517,11 +6599,17 @@
       <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -6536,7 +6624,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -6544,7 +6632,7 @@
     </row>
     <row r="16" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>210</v>
@@ -6552,11 +6640,17 @@
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -6571,7 +6665,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -6579,7 +6673,7 @@
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>211</v>
@@ -6587,11 +6681,17 @@
       <c r="C17" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -6606,7 +6706,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -6614,7 +6714,7 @@
     </row>
     <row r="18" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>212</v>
@@ -6622,11 +6722,17 @@
       <c r="C18" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -6641,7 +6747,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -6649,7 +6755,7 @@
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>213</v>
@@ -6657,11 +6763,17 @@
       <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -6676,7 +6788,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -6684,7 +6796,7 @@
     </row>
     <row r="20" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>214</v>
@@ -6692,11 +6804,17 @@
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -6711,7 +6829,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -6719,7 +6837,7 @@
     </row>
     <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>215</v>
@@ -6727,11 +6845,17 @@
       <c r="C21" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -6746,7 +6870,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -6754,7 +6878,7 @@
     </row>
     <row r="22" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>216</v>
@@ -6762,11 +6886,17 @@
       <c r="C22" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F22" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -6781,7 +6911,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -6789,7 +6919,7 @@
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>217</v>
@@ -6797,11 +6927,17 @@
       <c r="C23" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F23" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -6816,7 +6952,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>16</v>
@@ -6824,7 +6960,7 @@
     </row>
     <row r="24" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>218</v>
@@ -6832,11 +6968,17 @@
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F24" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -6851,7 +6993,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>16</v>
@@ -6859,19 +7001,25 @@
     </row>
     <row r="25" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -6886,7 +7034,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>16</v>
@@ -6894,7 +7042,7 @@
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>219</v>
@@ -6902,11 +7050,17 @@
       <c r="C26" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F26" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -6921,7 +7075,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>16</v>
@@ -6929,7 +7083,7 @@
     </row>
     <row r="27" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>220</v>
@@ -6937,11 +7091,17 @@
       <c r="C27" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F27" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -6956,7 +7116,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>16</v>
@@ -6964,7 +7124,7 @@
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>221</v>
@@ -6972,11 +7132,17 @@
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -6991,7 +7157,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>16</v>
@@ -6999,7 +7165,7 @@
     </row>
     <row r="29" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>222</v>
@@ -7007,11 +7173,17 @@
       <c r="C29" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F29" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -7026,7 +7198,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>16</v>
@@ -7034,7 +7206,7 @@
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>223</v>
@@ -7042,11 +7214,17 @@
       <c r="C30" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F30" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -7061,7 +7239,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>16</v>
@@ -7069,7 +7247,7 @@
     </row>
     <row r="31" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>224</v>
@@ -7077,11 +7255,17 @@
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -7096,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>16</v>
@@ -7104,19 +7288,25 @@
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>225</v>
+        <v>451</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F32" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -7131,7 +7321,7 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>16</v>
@@ -7139,19 +7329,25 @@
     </row>
     <row r="33" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -7166,7 +7362,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>16</v>
@@ -7174,19 +7370,25 @@
     </row>
     <row r="34" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -7201,7 +7403,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>16</v>
@@ -7209,19 +7411,25 @@
     </row>
     <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -7236,7 +7444,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>16</v>
@@ -7244,19 +7452,25 @@
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D36" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F36" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -7271,7 +7485,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>16</v>
@@ -7279,19 +7493,25 @@
     </row>
     <row r="37" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -7306,7 +7526,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>16</v>
@@ -7361,7 +7581,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -7376,10 +7596,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -7390,16 +7610,22 @@
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -7414,27 +7640,33 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -7449,27 +7681,33 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -7484,27 +7722,33 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -7519,27 +7763,33 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -7554,27 +7804,33 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -7589,27 +7845,33 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -7624,27 +7886,33 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F9" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -7659,27 +7927,33 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="248" customHeight="1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -7694,27 +7968,33 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F11" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -7729,27 +8009,33 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F12" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -7764,27 +8050,33 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F13" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -7799,27 +8091,33 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="272" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F14" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -7834,27 +8132,33 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F15" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -7869,27 +8173,33 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F16" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -7904,27 +8214,33 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F17" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -7939,27 +8255,33 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F18" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -7974,27 +8296,33 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F19" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -8009,27 +8337,33 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>247</v>
+        <v>453</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F20" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -8044,27 +8378,33 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F21" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -8079,27 +8419,33 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F22" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -8114,27 +8460,33 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F23" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -8149,27 +8501,33 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="323" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>251</v>
+        <v>454</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D24" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F24" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -8184,27 +8542,33 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F25" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -8219,27 +8583,33 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="356" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -8254,27 +8624,33 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F27" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -8289,27 +8665,33 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F28" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -8324,27 +8706,33 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -8359,27 +8747,33 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F30" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -8394,27 +8788,33 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F31" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -8429,27 +8829,33 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D32" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F32" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -8464,27 +8870,33 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D33" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F33" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -8499,15 +8911,15 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
@@ -8515,11 +8927,17 @@
       <c r="C34" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F34" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -8534,27 +8952,33 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F35" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -8569,27 +8993,33 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D36" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F36" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -8604,27 +9034,33 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D37" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F37" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -8639,27 +9075,33 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>13</v>
@@ -8674,27 +9116,33 @@
         <v>10</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>13</v>
@@ -8709,27 +9157,33 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -8744,27 +9198,33 @@
         <v>10</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D41" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>13</v>
@@ -8779,10 +9239,10 @@
         <v>10</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -8831,7 +9291,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -8846,10 +9306,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -8860,7 +9320,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
@@ -8875,7 +9335,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -8890,7 +9350,7 @@
         <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -8898,10 +9358,10 @@
     </row>
     <row r="3" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>64</v>
@@ -8916,7 +9376,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -8931,7 +9391,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -8939,19 +9399,25 @@
     </row>
     <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -8966,7 +9432,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -8974,19 +9440,25 @@
     </row>
     <row r="5" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -9001,7 +9473,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -9009,19 +9481,25 @@
     </row>
     <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -9036,27 +9514,33 @@
         <v>18</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -9071,7 +9555,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -9079,19 +9563,25 @@
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -9106,27 +9596,33 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -9141,7 +9637,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -9149,19 +9645,25 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -9176,7 +9678,7 @@
         <v>18</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -9184,19 +9686,25 @@
     </row>
     <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -9211,7 +9719,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -9219,19 +9727,25 @@
     </row>
     <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -9246,7 +9760,7 @@
         <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -9254,19 +9768,25 @@
     </row>
     <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -9281,7 +9801,7 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -9289,19 +9809,25 @@
     </row>
     <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -9316,7 +9842,7 @@
         <v>18</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -9324,19 +9850,25 @@
     </row>
     <row r="15" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -9351,7 +9883,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -9359,19 +9891,25 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -9386,7 +9924,7 @@
         <v>18</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -9394,19 +9932,25 @@
     </row>
     <row r="17" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -9421,7 +9965,7 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -9429,19 +9973,25 @@
     </row>
     <row r="18" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -9456,7 +10006,7 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -9464,19 +10014,25 @@
     </row>
     <row r="19" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -9491,7 +10047,7 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -9499,19 +10055,25 @@
     </row>
     <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -9526,7 +10088,7 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -9534,19 +10096,25 @@
     </row>
     <row r="21" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -9561,7 +10129,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -9569,19 +10137,25 @@
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -9596,7 +10170,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -9648,7 +10222,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -9663,10 +10237,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -9677,7 +10251,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
@@ -9692,7 +10266,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -9707,7 +10281,7 @@
         <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -9715,10 +10289,10 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
@@ -9733,7 +10307,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -9748,7 +10322,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -9756,10 +10330,10 @@
     </row>
     <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
@@ -9774,7 +10348,7 @@
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -9789,7 +10363,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -9797,10 +10371,10 @@
     </row>
     <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -9815,7 +10389,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -9830,7 +10404,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -9838,10 +10412,10 @@
     </row>
     <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
@@ -9856,7 +10430,7 @@
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -9871,7 +10445,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -9879,10 +10453,10 @@
     </row>
     <row r="7" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
@@ -9897,7 +10471,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -9912,7 +10486,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -9920,10 +10494,10 @@
     </row>
     <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -9938,7 +10512,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -9953,7 +10527,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -9961,10 +10535,10 @@
     </row>
     <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
@@ -9979,7 +10553,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -9994,7 +10568,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -10002,10 +10576,10 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>65</v>
@@ -10020,7 +10594,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -10035,7 +10609,7 @@
         <v>18</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -10043,10 +10617,10 @@
     </row>
     <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
@@ -10061,7 +10635,7 @@
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -10076,7 +10650,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -10084,10 +10658,10 @@
     </row>
     <row r="12" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
@@ -10102,7 +10676,7 @@
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -10117,7 +10691,7 @@
         <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -10125,10 +10699,10 @@
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>65</v>
@@ -10143,7 +10717,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -10158,7 +10732,7 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -10166,10 +10740,10 @@
     </row>
     <row r="14" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
@@ -10181,7 +10755,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -10196,7 +10770,7 @@
         <v>18</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -10204,10 +10778,10 @@
     </row>
     <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>64</v>
@@ -10222,7 +10796,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -10237,7 +10811,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -10245,10 +10819,10 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>65</v>
@@ -10263,7 +10837,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -10278,7 +10852,7 @@
         <v>18</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -10286,10 +10860,10 @@
     </row>
     <row r="17" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
@@ -10304,7 +10878,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -10319,7 +10893,7 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -10327,16 +10901,16 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>67</v>
@@ -10345,7 +10919,7 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -10360,7 +10934,7 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -10368,10 +10942,10 @@
     </row>
     <row r="19" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>64</v>
@@ -10386,7 +10960,7 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -10401,7 +10975,7 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -10409,16 +10983,16 @@
     </row>
     <row r="20" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>67</v>
@@ -10427,7 +11001,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -10442,7 +11016,7 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
@@ -10450,10 +11024,10 @@
     </row>
     <row r="21" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
@@ -10468,7 +11042,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -10483,7 +11057,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -10491,10 +11065,10 @@
     </row>
     <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
@@ -10509,7 +11083,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -10524,7 +11098,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
